--- a/task450/golden/grade5_math_results_2026.xlsx
+++ b/task450/golden/grade5_math_results_2026.xlsx
@@ -710,10 +710,10 @@
         <v>116</v>
       </c>
       <c r="E4" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" s="4">
-        <v>34.5</v>
+        <v>33.6</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -733,10 +733,10 @@
         <v>138</v>
       </c>
       <c r="E5" s="3">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F5" s="4">
-        <v>48.6</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -776,10 +776,10 @@
         <v>129</v>
       </c>
       <c r="E7" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" s="4">
-        <v>45</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -816,10 +816,10 @@
         <v>130</v>
       </c>
       <c r="E9" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="4">
-        <v>41.5</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -836,10 +836,10 @@
         <v>66</v>
       </c>
       <c r="E10" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" s="4">
-        <v>34.8</v>
+        <v>33.3</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -859,10 +859,10 @@
         <v>105</v>
       </c>
       <c r="E11" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="4">
-        <v>55.2</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -879,10 +879,10 @@
         <v>149</v>
       </c>
       <c r="E12" s="3">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F12" s="4">
-        <v>43.6</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -939,10 +939,10 @@
         <v>124</v>
       </c>
       <c r="E15" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F15" s="4">
-        <v>43.5</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -959,13 +959,10 @@
         <v>137</v>
       </c>
       <c r="E16" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F16" s="4">
-        <v>33.6</v>
-      </c>
-      <c r="G16" t="s">
-        <v>10</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -982,10 +979,10 @@
         <v>106</v>
       </c>
       <c r="E17" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F17" s="4">
-        <v>45.3</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1002,10 +999,10 @@
         <v>75</v>
       </c>
       <c r="E18" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18" s="4">
-        <v>44</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1022,10 +1019,10 @@
         <v>75</v>
       </c>
       <c r="E19" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19" s="4">
-        <v>44</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1042,10 +1039,10 @@
         <v>137</v>
       </c>
       <c r="E20" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F20" s="4">
-        <v>28.5</v>
+        <v>29.9</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
@@ -1065,10 +1062,10 @@
         <v>112</v>
       </c>
       <c r="E21" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F21" s="4">
-        <v>42.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1085,10 +1082,10 @@
         <v>103</v>
       </c>
       <c r="E22" s="3">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F22" s="4">
-        <v>32</v>
+        <v>35.9</v>
       </c>
       <c r="G22" t="s">
         <v>10</v>
@@ -1108,10 +1105,10 @@
         <v>108</v>
       </c>
       <c r="E23" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F23" s="4">
-        <v>45.4</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1148,10 +1145,10 @@
         <v>97</v>
       </c>
       <c r="E25" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" s="4">
-        <v>42.3</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1168,10 +1165,10 @@
         <v>100</v>
       </c>
       <c r="E26" s="3">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F26" s="4">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1188,10 +1185,10 @@
         <v>113</v>
       </c>
       <c r="E27" s="3">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F27" s="4">
-        <v>56.6</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1228,10 +1225,10 @@
         <v>55</v>
       </c>
       <c r="E29" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" s="4">
-        <v>18.2</v>
+        <v>16.4</v>
       </c>
       <c r="G29" t="s">
         <v>10</v>
@@ -1251,10 +1248,10 @@
         <v>68</v>
       </c>
       <c r="E30" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F30" s="4">
-        <v>60.3</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1291,10 +1288,10 @@
         <v>121</v>
       </c>
       <c r="E32" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" s="4">
-        <v>72.7</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1311,10 +1308,10 @@
         <v>146</v>
       </c>
       <c r="E33" s="3">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F33" s="4">
-        <v>53.4</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1331,10 +1328,10 @@
         <v>64</v>
       </c>
       <c r="E34" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F34" s="4">
-        <v>35.9</v>
+        <v>34.4</v>
       </c>
       <c r="G34" t="s">
         <v>10</v>
@@ -1377,10 +1374,10 @@
         <v>143</v>
       </c>
       <c r="E36" s="3">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F36" s="4">
-        <v>73.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1417,10 +1414,10 @@
         <v>126</v>
       </c>
       <c r="E38" s="3">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F38" s="4">
-        <v>76.2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1437,10 +1434,10 @@
         <v>143</v>
       </c>
       <c r="E39" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F39" s="4">
-        <v>34.3</v>
+        <v>33.6</v>
       </c>
       <c r="G39" t="s">
         <v>10</v>
@@ -1460,10 +1457,10 @@
         <v>74</v>
       </c>
       <c r="E40" s="3">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F40" s="4">
-        <v>52.7</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1480,10 +1477,10 @@
         <v>76</v>
       </c>
       <c r="E41" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F41" s="4">
-        <v>65.8</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1500,10 +1497,10 @@
         <v>126</v>
       </c>
       <c r="E42" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F42" s="4">
-        <v>54</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1520,10 +1517,10 @@
         <v>87</v>
       </c>
       <c r="E43" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F43" s="4">
-        <v>70.09999999999999</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1540,10 +1537,10 @@
         <v>114</v>
       </c>
       <c r="E44" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F44" s="4">
-        <v>29.8</v>
+        <v>28.1</v>
       </c>
       <c r="G44" t="s">
         <v>10</v>
@@ -1583,10 +1580,10 @@
         <v>65</v>
       </c>
       <c r="E46" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F46" s="4">
-        <v>30.8</v>
+        <v>27.7</v>
       </c>
       <c r="G46" t="s">
         <v>10</v>
@@ -1606,10 +1603,10 @@
         <v>82</v>
       </c>
       <c r="E47" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F47" s="4">
-        <v>48.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1626,10 +1623,10 @@
         <v>65</v>
       </c>
       <c r="E48" s="3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F48" s="4">
-        <v>47.7</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1646,10 +1643,10 @@
         <v>131</v>
       </c>
       <c r="E49" s="3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F49" s="4">
-        <v>48.1</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1666,10 +1663,10 @@
         <v>176</v>
       </c>
       <c r="E50" s="3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F50" s="4">
-        <v>35.8</v>
+        <v>34.7</v>
       </c>
       <c r="G50" t="s">
         <v>10</v>
@@ -1689,10 +1686,10 @@
         <v>55</v>
       </c>
       <c r="E51" s="3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F51" s="4">
-        <v>67.3</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1709,10 +1706,13 @@
         <v>67</v>
       </c>
       <c r="E52" s="3">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F52" s="4">
-        <v>43.3</v>
+        <v>34.3</v>
+      </c>
+      <c r="G52" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1729,10 +1729,10 @@
         <v>117</v>
       </c>
       <c r="E53" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F53" s="4">
-        <v>37.6</v>
+        <v>36.8</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -1752,10 +1752,10 @@
         <v>100</v>
       </c>
       <c r="E54" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F54" s="4">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -1772,10 +1772,10 @@
         <v>132</v>
       </c>
       <c r="E55" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F55" s="4">
-        <v>13.6</v>
+        <v>12.9</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -1795,10 +1795,10 @@
         <v>92</v>
       </c>
       <c r="E56" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F56" s="4">
-        <v>70.7</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -1815,10 +1815,10 @@
         <v>98</v>
       </c>
       <c r="E57" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F57" s="4">
-        <v>72.40000000000001</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -1831,10 +1831,10 @@
         <v>5727</v>
       </c>
       <c r="E58" s="6">
-        <v>2769</v>
+        <v>2745</v>
       </c>
       <c r="F58" s="7">
-        <v>48.3</v>
+        <v>47.9</v>
       </c>
       <c r="G58" s="5">
         <v>15</v>
